--- a/artfynd/A 61937-2022 artfynd.xlsx
+++ b/artfynd/A 61937-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61937-2022 artfynd.xlsx
+++ b/artfynd/A 61937-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104025759</v>
+        <v>111337416</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549689.4155546706</v>
+        <v>549746</v>
       </c>
       <c r="R2" t="n">
-        <v>7004187.747964761</v>
+        <v>7004213</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,69 +761,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104025724</v>
+        <v>111337018</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549779.9783267922</v>
+        <v>549790</v>
       </c>
       <c r="R3" t="n">
-        <v>7004154.794694394</v>
+        <v>7004216</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,40 +855,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104025739</v>
+        <v>111343423</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,37 +882,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549323.908588615</v>
+        <v>549781</v>
       </c>
       <c r="R4" t="n">
-        <v>7004296.937704899</v>
+        <v>7004218</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,74 +957,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104025729</v>
+        <v>111336038</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549282.8535943135</v>
+        <v>549625</v>
       </c>
       <c r="R5" t="n">
-        <v>7004318.454888589</v>
+        <v>7004276</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,31 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104025762</v>
+        <v>111336614</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,37 +1078,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549358.1433440853</v>
+        <v>549796</v>
       </c>
       <c r="R6" t="n">
-        <v>7004277.576299956</v>
+        <v>7004183</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,53 +1153,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104025712</v>
+        <v>104025710</v>
       </c>
       <c r="B7" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549673.0211805711</v>
+        <v>549684</v>
       </c>
       <c r="R7" t="n">
-        <v>7004135.524965952</v>
+        <v>7004188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1235,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1245,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,15 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104025773</v>
+        <v>111336227</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,37 +1287,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549674.3950348584</v>
+        <v>549658</v>
       </c>
       <c r="R8" t="n">
-        <v>7004193.392149226</v>
+        <v>7004283</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,31 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104025770</v>
+        <v>104025759</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549288.6385768012</v>
+        <v>549690</v>
       </c>
       <c r="R9" t="n">
-        <v>7004324.86964185</v>
+        <v>7004188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1444,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1454,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104025778</v>
+        <v>111337274</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,37 +1496,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549288.7763039864</v>
+        <v>549771</v>
       </c>
       <c r="R10" t="n">
-        <v>7004315.833762431</v>
+        <v>7004204</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,22 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,69 +1571,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104025760</v>
+        <v>111338395</v>
       </c>
       <c r="B11" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549718.5866170209</v>
+        <v>549687</v>
       </c>
       <c r="R11" t="n">
-        <v>7004174.186788636</v>
+        <v>7004207</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,22 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,40 +1665,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104025728</v>
+        <v>111343076</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,37 +1692,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549718.5449389962</v>
+        <v>549465</v>
       </c>
       <c r="R12" t="n">
-        <v>7004176.897674919</v>
+        <v>7004184</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,22 +1747,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,62 +1763,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104025743</v>
+        <v>104025739</v>
       </c>
       <c r="B13" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549461.9240521474</v>
+        <v>549324</v>
       </c>
       <c r="R13" t="n">
-        <v>7004238.038358305</v>
+        <v>7004297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +1849,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,7 +1859,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,53 +1890,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104025747</v>
+        <v>111343126</v>
       </c>
       <c r="B14" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229748</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549366.1351752024</v>
+        <v>549593</v>
       </c>
       <c r="R14" t="n">
-        <v>7004287.64019315</v>
+        <v>7004142</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,22 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,78 +1972,65 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104025710</v>
+        <v>111343343</v>
       </c>
       <c r="B15" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Granåsbäcken, Jmt</t>
+          <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549684.4387889371</v>
+        <v>549669</v>
       </c>
       <c r="R15" t="n">
-        <v>7004187.671498715</v>
+        <v>7004184</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2278,22 +2054,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,31 +2074,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104025769</v>
+        <v>104025743</v>
       </c>
       <c r="B16" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,21 +2097,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2121,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549779.9783267922</v>
+        <v>549462</v>
       </c>
       <c r="R16" t="n">
-        <v>7004154.794694394</v>
+        <v>7004238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2399,7 +2156,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2409,7 +2166,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,11 +2177,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2445,19 +2197,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111337565</v>
+        <v>104025770</v>
       </c>
       <c r="B17" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2479,20 +2226,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549715.6348940523</v>
+        <v>549289</v>
       </c>
       <c r="R17" t="n">
-        <v>7004160.131816954</v>
+        <v>7004325</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2516,22 +2262,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,49 +2292,48 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111337534</v>
+        <v>111335971</v>
       </c>
       <c r="B18" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549727.6978484992</v>
+        <v>549618</v>
       </c>
       <c r="R18" t="n">
-        <v>7004170.259585364</v>
+        <v>7004285</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2632,19 +2377,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,37 +2406,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111338395</v>
+        <v>111336124</v>
       </c>
       <c r="B19" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2712,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549687.3142575396</v>
+        <v>549639</v>
       </c>
       <c r="R19" t="n">
-        <v>7004206.696234533</v>
+        <v>7004266</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2745,19 +2475,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,19 +2504,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111336392</v>
+        <v>111336228</v>
       </c>
       <c r="B20" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2825,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549746.1391566205</v>
+        <v>549658</v>
       </c>
       <c r="R20" t="n">
-        <v>7004295.271288151</v>
+        <v>7004283</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2858,19 +2573,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,37 +2602,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111336113</v>
+        <v>111336273</v>
       </c>
       <c r="B21" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549651.5405950209</v>
+        <v>549684</v>
       </c>
       <c r="R21" t="n">
-        <v>7004267.154941834</v>
+        <v>7004279</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2971,19 +2671,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,37 +2700,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111337617</v>
+        <v>111336392</v>
       </c>
       <c r="B22" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3051,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549731.7759114051</v>
+        <v>549746</v>
       </c>
       <c r="R22" t="n">
-        <v>7004140.495309836</v>
+        <v>7004295</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3084,19 +2769,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,19 +2798,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111337813</v>
+        <v>111336447</v>
       </c>
       <c r="B23" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3164,10 +2834,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549700.3448335464</v>
+        <v>549749</v>
       </c>
       <c r="R23" t="n">
-        <v>7004036.067456141</v>
+        <v>7004235</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3197,24 +2867,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,16 +2899,11 @@
         <v>111337343</v>
       </c>
       <c r="B24" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3282,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549727.9287928357</v>
+        <v>549728</v>
       </c>
       <c r="R24" t="n">
-        <v>7004214.099270299</v>
+        <v>7004214</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3315,19 +2965,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,37 +2994,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111337707</v>
+        <v>111337565</v>
       </c>
       <c r="B25" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3395,10 +3030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549705.8447932284</v>
+        <v>549716</v>
       </c>
       <c r="R25" t="n">
-        <v>7004061.00861726</v>
+        <v>7004160</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3428,19 +3063,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,37 +3092,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111336335</v>
+        <v>111337675</v>
       </c>
       <c r="B26" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3508,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549707.3631376704</v>
+        <v>549723</v>
       </c>
       <c r="R26" t="n">
-        <v>7004286.088810139</v>
+        <v>7004114</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3541,19 +3161,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3580,15 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111338057</v>
+        <v>111337813</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3621,10 +3226,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549695.6594417326</v>
+        <v>549700</v>
       </c>
       <c r="R27" t="n">
-        <v>7004017.013898557</v>
+        <v>7004036</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3654,19 +3259,14 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3693,15 +3293,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111336227</v>
+        <v>104025762</v>
       </c>
       <c r="B28" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3709,38 +3304,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549658.0979739621</v>
+        <v>549358</v>
       </c>
       <c r="R28" t="n">
-        <v>7004282.168564727</v>
+        <v>7004278</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,22 +3358,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,27 +3388,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111337850</v>
+        <v>104025773</v>
       </c>
       <c r="B29" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3822,38 +3415,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549695.6594417326</v>
+        <v>549674</v>
       </c>
       <c r="R29" t="n">
-        <v>7004017.013898557</v>
+        <v>7004194</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3877,22 +3469,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,27 +3499,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111336211</v>
+        <v>104025778</v>
       </c>
       <c r="B30" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,38 +3526,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549658.0979739621</v>
+        <v>549289</v>
       </c>
       <c r="R30" t="n">
-        <v>7004282.168564727</v>
+        <v>7004316</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3990,22 +3580,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4020,27 +3610,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111337274</v>
+        <v>104025724</v>
       </c>
       <c r="B31" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,38 +3637,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549771.062580543</v>
+        <v>549780</v>
       </c>
       <c r="R31" t="n">
-        <v>7004204.820678852</v>
+        <v>7004155</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4103,22 +3691,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,70 +3717,73 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111337155</v>
+        <v>104025728</v>
       </c>
       <c r="B32" t="n">
-        <v>96674</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549780.8143631967</v>
+        <v>549718</v>
       </c>
       <c r="R32" t="n">
-        <v>7004218.076358073</v>
+        <v>7004177</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4216,22 +3807,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4242,31 +3833,35 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111337732</v>
+        <v>111335966</v>
       </c>
       <c r="B33" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4299,10 +3894,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549717.9984537691</v>
+        <v>549618</v>
       </c>
       <c r="R33" t="n">
-        <v>7004065.262869562</v>
+        <v>7004285</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4332,19 +3927,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4371,15 +3956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111336124</v>
+        <v>111336113</v>
       </c>
       <c r="B34" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,21 +3967,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4412,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549639.3390683155</v>
+        <v>549652</v>
       </c>
       <c r="R34" t="n">
-        <v>7004266.063804692</v>
+        <v>7004267</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4445,19 +4025,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4484,15 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111337675</v>
+        <v>111336211</v>
       </c>
       <c r="B35" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4500,21 +4065,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4525,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549723.1300350486</v>
+        <v>549658</v>
       </c>
       <c r="R35" t="n">
-        <v>7004114.150543886</v>
+        <v>7004283</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4558,19 +4123,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,15 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111338753</v>
+        <v>111336335</v>
       </c>
       <c r="B36" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4638,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549613.6355042638</v>
+        <v>549707</v>
       </c>
       <c r="R36" t="n">
-        <v>7004171.671098326</v>
+        <v>7004286</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4671,19 +4221,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4710,15 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111336273</v>
+        <v>111337534</v>
       </c>
       <c r="B37" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4726,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4751,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549684.3799834364</v>
+        <v>549728</v>
       </c>
       <c r="R37" t="n">
-        <v>7004279.860827052</v>
+        <v>7004170</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4784,19 +4319,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4823,37 +4348,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111337327</v>
+        <v>111337584</v>
       </c>
       <c r="B38" t="n">
-        <v>96674</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4864,10 +4384,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>549727.9287928357</v>
+        <v>549716</v>
       </c>
       <c r="R38" t="n">
-        <v>7004214.099270299</v>
+        <v>7004160</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4897,19 +4417,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4936,37 +4446,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111337759</v>
+        <v>111337617</v>
       </c>
       <c r="B39" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4482,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549717.9984537691</v>
+        <v>549732</v>
       </c>
       <c r="R39" t="n">
-        <v>7004065.262869562</v>
+        <v>7004140</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5010,19 +4515,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,12 +4547,7 @@
         <v>111337702</v>
       </c>
       <c r="B40" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5090,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549723.1300350486</v>
+        <v>549723</v>
       </c>
       <c r="R40" t="n">
-        <v>7004114.150543886</v>
+        <v>7004114</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5123,19 +4613,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5162,15 +4642,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111337584</v>
+        <v>111337707</v>
       </c>
       <c r="B41" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5203,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>549715.6348940523</v>
+        <v>549706</v>
       </c>
       <c r="R41" t="n">
-        <v>7004160.131816954</v>
+        <v>7004061</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,19 +4711,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5275,37 +4740,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111338251</v>
+        <v>111337732</v>
       </c>
       <c r="B42" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5316,10 +4776,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549727.6978484992</v>
+        <v>549718</v>
       </c>
       <c r="R42" t="n">
-        <v>7004170.259585364</v>
+        <v>7004065</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5349,19 +4809,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5388,15 +4838,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111338802</v>
+        <v>111337850</v>
       </c>
       <c r="B43" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5429,10 +4874,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549582.1286667091</v>
+        <v>549696</v>
       </c>
       <c r="R43" t="n">
-        <v>7004219.543078575</v>
+        <v>7004017</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5462,19 +4907,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5501,15 +4936,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111336447</v>
+        <v>111337907</v>
       </c>
       <c r="B44" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5517,21 +4947,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5542,10 +4972,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549749.7920083915</v>
+        <v>549719</v>
       </c>
       <c r="R44" t="n">
-        <v>7004234.319783674</v>
+        <v>7003970</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5575,19 +5005,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5614,37 +5034,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111336038</v>
+        <v>111338753</v>
       </c>
       <c r="B45" t="n">
-        <v>96253</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5655,10 +5070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549625.1614441903</v>
+        <v>549613</v>
       </c>
       <c r="R45" t="n">
-        <v>7004275.788168156</v>
+        <v>7004172</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5688,19 +5103,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5727,15 +5132,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111337416</v>
+        <v>111338802</v>
       </c>
       <c r="B46" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5743,21 +5143,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5768,10 +5168,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549746.0398758095</v>
+        <v>549582</v>
       </c>
       <c r="R46" t="n">
-        <v>7004213.473991236</v>
+        <v>7004220</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5801,19 +5201,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,15 +5230,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111336614</v>
+        <v>111342489</v>
       </c>
       <c r="B47" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5856,21 +5241,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5881,10 +5266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549795.3823130414</v>
+        <v>549579</v>
       </c>
       <c r="R47" t="n">
-        <v>7004183.051039582</v>
+        <v>7004203</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5911,22 +5296,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5953,15 +5328,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111336228</v>
+        <v>111342984</v>
       </c>
       <c r="B48" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5969,21 +5339,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5994,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549658.0979739621</v>
+        <v>549369</v>
       </c>
       <c r="R48" t="n">
-        <v>7004282.168564727</v>
+        <v>7004217</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6024,22 +5394,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6066,37 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111343343</v>
+        <v>111343048</v>
       </c>
       <c r="B49" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6107,10 +5462,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>549668.6522002188</v>
+        <v>549479</v>
       </c>
       <c r="R49" t="n">
-        <v>7004184.265558192</v>
+        <v>7004125</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6140,19 +5495,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,37 +5524,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111343423</v>
+        <v>111343511</v>
       </c>
       <c r="B50" t="n">
-        <v>73688</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6220,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>549780.8143631967</v>
+        <v>549769</v>
       </c>
       <c r="R50" t="n">
-        <v>7004218.076358073</v>
+        <v>7004271</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6253,19 +5593,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6292,15 +5622,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111343076</v>
+        <v>111343523</v>
       </c>
       <c r="B51" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6308,21 +5633,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6333,10 +5658,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>549465.4679211122</v>
+        <v>549746</v>
       </c>
       <c r="R51" t="n">
-        <v>7004183.862762679</v>
+        <v>7004264</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6366,19 +5691,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,37 +5720,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111343126</v>
+        <v>111337759</v>
       </c>
       <c r="B52" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6446,10 +5756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>549592.8283332227</v>
+        <v>549718</v>
       </c>
       <c r="R52" t="n">
-        <v>7004141.525011718</v>
+        <v>7004065</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6476,22 +5786,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,54 +5818,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111343523</v>
+        <v>104025769</v>
       </c>
       <c r="B53" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>549746.6117757267</v>
+        <v>549780</v>
       </c>
       <c r="R53" t="n">
-        <v>7004264.548898073</v>
+        <v>7004155</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6589,22 +5883,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6615,31 +5909,35 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111342489</v>
+        <v>104025729</v>
       </c>
       <c r="B54" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6647,38 +5945,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549579.2110328446</v>
+        <v>549283</v>
       </c>
       <c r="R54" t="n">
-        <v>7004203.229387118</v>
+        <v>7004319</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6702,22 +6004,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6732,63 +6034,67 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111343511</v>
+        <v>111337909</v>
       </c>
       <c r="B55" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>549768.2237563633</v>
+        <v>549719</v>
       </c>
       <c r="R55" t="n">
-        <v>7004271.660066182</v>
+        <v>7003970</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6815,22 +6121,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6857,54 +6153,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111342984</v>
+        <v>104025712</v>
       </c>
       <c r="B56" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomsterbodarna, Jmt</t>
+          <t>Granåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>549369.0277540553</v>
+        <v>549673</v>
       </c>
       <c r="R56" t="n">
-        <v>7004216.734669155</v>
+        <v>7004136</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6928,22 +6218,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6958,27 +6248,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111342736</v>
+        <v>111336083</v>
       </c>
       <c r="B57" t="n">
-        <v>96674</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,21 +6275,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7011,10 +6300,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>549447.1702291399</v>
+        <v>549633</v>
       </c>
       <c r="R57" t="n">
-        <v>7004196.688548212</v>
+        <v>7004283</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7041,22 +6330,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7083,37 +6362,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111337018</v>
+        <v>111338251</v>
       </c>
       <c r="B58" t="n">
-        <v>73688</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>492</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7124,10 +6398,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>549789.8977257085</v>
+        <v>549728</v>
       </c>
       <c r="R58" t="n">
-        <v>7004215.9566198</v>
+        <v>7004170</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7157,19 +6431,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7196,57 +6460,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111516947</v>
+        <v>111336713</v>
       </c>
       <c r="B59" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blomsterbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>549706.8608092552</v>
+        <v>549781</v>
       </c>
       <c r="R59" t="n">
-        <v>7004053.793232109</v>
+        <v>7004218</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7273,28 +6529,17 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7310,6 +6555,843 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>111337327</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>549728</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7004214</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>111342736</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>549447</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7004196</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>104024369</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>549204</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7004275</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>111338057</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>549696</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7004017</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>111516947</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>549707</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7004054</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>111338000</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Blomsterbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>549734</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003977</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>104025760</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Granåsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>549718</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7004174</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>104025747</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Granåsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>549366</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7004288</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61937-2022 artfynd.xlsx
+++ b/artfynd/A 61937-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337416</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336614</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025710</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337274</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338395</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343076</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025739</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343126</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343343</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2194,6 +2269,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025743</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025770</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,6 +2488,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335971</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2501,6 +2591,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336124</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336228</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336392</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2893,6 +3003,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336447</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337343</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3089,6 +3209,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337565</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3187,6 +3312,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337675</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3290,6 +3420,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337813</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3401,6 +3536,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025762</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3512,6 +3652,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025773</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3623,6 +3768,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025778</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3739,6 +3889,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025724</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3855,6 +4010,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025728</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3953,6 +4113,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111335966</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4051,6 +4216,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336113</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4149,6 +4319,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336211</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4247,6 +4422,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336335</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4345,6 +4525,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337534</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4443,6 +4628,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337584</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4541,6 +4731,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337617</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,6 +4834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337702</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4737,6 +4937,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337707</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4835,6 +5040,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337732</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4933,6 +5143,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337850</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5031,6 +5246,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337907</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5129,6 +5349,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338753</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5227,6 +5452,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338802</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5325,6 +5555,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111342489</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5423,6 +5658,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111342984</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5521,6 +5761,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5619,6 +5864,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343511</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5717,6 +5967,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111343523</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5815,6 +6070,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337759</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5931,6 +6191,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025769</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6047,6 +6312,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025729</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6150,6 +6420,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337909</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6261,6 +6536,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025712</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6359,6 +6639,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336083</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6457,6 +6742,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338251</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6555,6 +6845,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111336713</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6653,6 +6948,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111337327</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6751,6 +7051,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111342736</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6862,6 +7167,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104024369</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6960,6 +7270,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338057</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7062,6 +7377,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111516947</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7160,6 +7480,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111338000</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7276,6 +7601,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025760</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7392,8 +7722,81 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>